--- a/data/ams_weekly_data/Tonor/business_report_week33.xlsx
+++ b/data/ams_weekly_data/Tonor/business_report_week33.xlsx
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>67585.39</v>
+        <v>85201.42999999999</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -854,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>2075.42</v>
+        <v>4150.84</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -925,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>31990.67</v>
+        <v>34062.7</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>24756.82</v>
+        <v>26517.84</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>4506.78</v>
+        <v>9013.549999999999</v>
       </c>
       <c r="U16">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>1948.31</v>
+        <v>3896.62</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -2055,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>15205.92</v>
+        <v>18587.28</v>
       </c>
       <c r="U20">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="T21">
-        <v>23510.2</v>
+        <v>25834.78</v>
       </c>
       <c r="U21">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>23752.55</v>
+        <v>25446.62</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2327,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>24393.28</v>
+        <v>30491.6</v>
       </c>
       <c r="U24">
         <v>0</v>
